--- a/objects/any_cancer.xlsx
+++ b/objects/any_cancer.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t xml:space="preserve">model</t>
   </si>
@@ -20,6 +20,9 @@
     <t xml:space="preserve">term</t>
   </si>
   <si>
+    <t xml:space="preserve">Severe COVID</t>
+  </si>
+  <si>
     <t xml:space="preserve">Hospitalized</t>
   </si>
   <si>
@@ -35,55 +38,67 @@
     <t xml:space="preserve">1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95 (1.80, 2.10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50 (1.31, 1.73)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13 (2.65, 3.68)</t>
+    <t xml:space="preserve">2.12 (1.98, 2.27)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97 (1.84, 2.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53 (1.34, 1.75)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18 (2.72, 3.71)</t>
   </si>
   <si>
     <t xml:space="preserve">unadjusted_firth</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51 (1.31, 1.73)</t>
+    <t xml:space="preserve">1.98 (1.84, 2.12)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.21 (1.11, 1.31)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.93 (0.80, 1.08)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31 (1.10, 1.55)</t>
+    <t xml:space="preserve">1.26 (1.17, 1.35)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22 (1.13, 1.32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94 (0.81, 1.09)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31 (1.11, 1.54)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">1.28 (1.17, 1.40)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95 (0.81, 1.11)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.29 (1.07, 1.55)</t>
+    <t xml:space="preserve">1.32 (1.21, 1.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30 (1.19, 1.41)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96 (0.82, 1.12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23 (1.03, 1.47)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment3</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32 (1.19, 1.45)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24 (1.03, 1.49)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.32 (1.07, 1.63)</t>
+    <t xml:space="preserve">1.30 (1.19, 1.42)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30 (1.19, 1.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24 (1.04, 1.48)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23 (1.01, 1.49)</t>
   </si>
 </sst>
 </file>
@@ -428,90 +443,108 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s">
-        <v>19</v>
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>27</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/objects/any_cancer.xlsx
+++ b/objects/any_cancer.xlsx
@@ -59,25 +59,25 @@
     <t xml:space="preserve">adjustment1</t>
   </si>
   <si>
-    <t xml:space="preserve">1.26 (1.17, 1.35)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22 (1.13, 1.32)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94 (0.81, 1.09)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31 (1.11, 1.54)</t>
+    <t xml:space="preserve">1.26 (1.17, 1.36)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.23 (1.14, 1.33)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.94 (0.81, 1.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30 (1.11, 1.54)</t>
   </si>
   <si>
     <t xml:space="preserve">adjustment2</t>
   </si>
   <si>
-    <t xml:space="preserve">1.32 (1.21, 1.43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.30 (1.19, 1.41)</t>
+    <t xml:space="preserve">1.32 (1.22, 1.43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30 (1.20, 1.42)</t>
   </si>
   <si>
     <t xml:space="preserve">0.96 (0.82, 1.12)</t>
